--- a/core/src/main/resources/baseFiles/excel/Sheet.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="12000"/>
+    <workbookView windowWidth="29100" windowHeight="14520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1211,46 +1211,49 @@
   <sheetPr/>
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="3" max="3" width="12.6875"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:J397">
-    <sortCondition ref="D2:D397"/>
-    <sortCondition ref="J2:J397"/>
-    <sortCondition ref="I2:I397"/>
-    <sortCondition ref="F2:F397"/>
-    <sortCondition ref="C2:C397"/>
+  <sortState ref="A2:J452">
+    <sortCondition ref="D2:D452"/>
+    <sortCondition ref="J2:J452"/>
+    <sortCondition ref="I2:I452"/>
+    <sortCondition ref="F2:F452"/>
+    <sortCondition ref="C2:C452"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/core/src/main/resources/baseFiles/excel/Sheet.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Sheet.xlsx
@@ -1216,34 +1216,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
     </row>

--- a/core/src/main/resources/baseFiles/excel/Sheet.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="14520"/>
+    <workbookView windowWidth="29100" windowHeight="13560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1216,34 +1216,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/core/src/main/resources/baseFiles/excel/Sheet.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13560"/>
+    <workbookView windowWidth="23340" windowHeight="11980"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1216,34 +1216,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/core/src/main/resources/baseFiles/excel/Sheet.xlsx
+++ b/core/src/main/resources/baseFiles/excel/Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24680" windowHeight="13560"/>
+    <workbookView windowWidth="24680" windowHeight="13720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -689,7 +689,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1248,12 +1248,12 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:J452">
-    <sortCondition ref="D2:D452"/>
-    <sortCondition ref="J2:J452"/>
-    <sortCondition ref="I2:I452"/>
-    <sortCondition ref="F2:F452"/>
-    <sortCondition ref="C2:C452"/>
+  <sortState ref="A2:J380">
+    <sortCondition ref="D2:D380"/>
+    <sortCondition ref="J2:J380"/>
+    <sortCondition ref="I2:I380"/>
+    <sortCondition ref="F2:F380"/>
+    <sortCondition ref="C2:C380"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
